--- a/JD.xlsx
+++ b/JD.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75172E6B-2C2D-422E-A0F8-879E180F538E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB1249E-74BB-4BD2-80D6-1356B2B73451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14664" yWindow="2592" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2316" yWindow="2760" windowWidth="19176" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1058,6 +1058,7 @@
     <col min="5" max="5" width="41.77734375" customWidth="1"/>
     <col min="6" max="6" width="41.109375" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="18" max="18" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -1434,7 +1435,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1697,6 +1698,9 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
       <c r="B18" s="1"/>
       <c r="F18" s="3" t="s">
         <v>39</v>
@@ -1709,7 +1713,10 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
       <c r="B19" s="1"/>
       <c r="F19" s="3" t="s">
         <v>40</v>
@@ -1723,6 +1730,9 @@
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
       <c r="B20" s="1"/>
       <c r="F20" s="3" t="s">
         <v>41</v>
@@ -1733,6 +1743,9 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="F21" s="3" t="s">
         <v>42</v>
@@ -1743,6 +1756,9 @@
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
       <c r="B22" s="1"/>
       <c r="P22" s="1"/>
       <c r="R22" s="1" t="s">
@@ -1750,181 +1766,259 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
       <c r="B23" s="1"/>
       <c r="P23" s="1"/>
       <c r="R23" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
       <c r="B24" s="1"/>
       <c r="P24" s="1"/>
       <c r="R24" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
       <c r="B25" s="1"/>
       <c r="P25" s="1"/>
       <c r="R25" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
       <c r="B26" s="1"/>
       <c r="P26" s="1"/>
       <c r="R26" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
       <c r="B27" s="1"/>
       <c r="P27" s="1"/>
       <c r="R27" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
       <c r="B28" s="1"/>
       <c r="P28" s="1"/>
       <c r="R28" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
       <c r="B29" s="1"/>
       <c r="P29" s="1"/>
       <c r="R29" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
       <c r="B30" s="1"/>
       <c r="P30" s="1"/>
       <c r="R30" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
       <c r="B31" s="1"/>
       <c r="P31" s="1"/>
       <c r="R31" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
       <c r="B32" s="1"/>
       <c r="P32" s="1"/>
       <c r="R32" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
       <c r="B33" s="1"/>
       <c r="P33" s="1"/>
       <c r="R33" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
       <c r="B34" s="1"/>
       <c r="P34" s="1"/>
       <c r="R34" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
       <c r="B35" s="1"/>
       <c r="P35" s="1"/>
       <c r="R35" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="2:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
       <c r="B36" s="1"/>
       <c r="P36" s="1"/>
       <c r="R36" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
       <c r="B37" s="1"/>
       <c r="P37" s="1"/>
       <c r="R37" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
       <c r="B38" s="1"/>
       <c r="P38" s="1"/>
       <c r="R38" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="2:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
       <c r="B39" s="1"/>
       <c r="P39" s="1"/>
       <c r="R39" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
       <c r="B40" s="1"/>
       <c r="P40" s="1"/>
       <c r="R40" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="41" spans="2:18" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
       <c r="B41" s="1"/>
       <c r="P41" s="1"/>
       <c r="R41" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
       <c r="B42" s="1"/>
       <c r="P42" s="1"/>
       <c r="R42" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
       <c r="B43" s="1"/>
       <c r="P43" s="1"/>
       <c r="R43" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="2:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
       <c r="B44" s="1"/>
       <c r="P44" s="1"/>
       <c r="R44" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="45" spans="2:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
       <c r="B45" s="1"/>
       <c r="P45" s="1"/>
       <c r="R45" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="46" spans="2:18" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
       <c r="B46" s="1"/>
       <c r="P46" s="1"/>
       <c r="R46" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="47" spans="2:18" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
       <c r="B47" s="1"/>
       <c r="P47" s="1"/>
       <c r="R47" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
       <c r="B48" s="1"/>
       <c r="P48" s="1"/>
       <c r="R48" s="1" t="s">
